--- a/configurator-fotovoltaic/catalog_produse_pv.xlsx
+++ b/configurator-fotovoltaic/catalog_produse_pv.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tehni\Desktop\Gabi\CLAUDE oferta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{555D2A44-01E8-4302-840C-905FCE8AE792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3602670F-DD9B-4E59-B8C1-4C6BE8CC76A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14100" yWindow="2670" windowWidth="15375" windowHeight="11580" tabRatio="500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucțiuni" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="167">
   <si>
     <t>CATALOG PRODUSE PV — Ghid de utilizare</t>
   </si>
@@ -535,6 +535,9 @@
   </si>
   <si>
     <t>Trina</t>
+  </si>
+  <si>
+    <t>Powerbrick 16kw</t>
   </si>
 </sst>
 </file>
@@ -3096,13 +3099,27 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="8"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="8"/>
+      <c r="A13" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" s="10">
+        <v>16.07</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="F13" s="11">
+        <v>8978</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>

--- a/configurator-fotovoltaic/catalog_produse_pv.xlsx
+++ b/configurator-fotovoltaic/catalog_produse_pv.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tehni\Desktop\Gabi\CLAUDE oferta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tehni\Desktop\Gabi\CLAUDE oferta\Calculatorfotovoltaic\configurator-fotovoltaic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3602670F-DD9B-4E59-B8C1-4C6BE8CC76A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5802CF15-6CDC-43AD-B5FD-13C954188240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22650" yWindow="1680" windowWidth="14355" windowHeight="11760" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucțiuni" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="165">
   <si>
     <t>CATALOG PRODUSE PV — Ghid de utilizare</t>
   </si>
@@ -246,9 +246,6 @@
     <t>Goodwe</t>
   </si>
   <si>
-    <t>Invertor monofazat Goodwe GW3000-ES-20 3kW (LV)</t>
-  </si>
-  <si>
     <t>mono</t>
   </si>
   <si>
@@ -264,13 +261,7 @@
     <t>Invertor monofazat Goodwe GW6000-ES-20 6kW (LV)</t>
   </si>
   <si>
-    <t>Invertor monofazat Goodwe EH6000W HV 6kW (HV)</t>
-  </si>
-  <si>
     <t>hv</t>
-  </si>
-  <si>
-    <t>Invertor trifazat Goodwe GW5KN-ET HV 5kW (HV)</t>
   </si>
   <si>
     <t>tri</t>
@@ -537,7 +528,10 @@
     <t>Trina</t>
   </si>
   <si>
-    <t>Powerbrick 16kw</t>
+    <t>Trina bifacial 445</t>
+  </si>
+  <si>
+    <t>Invertor trifazat Goodwe GW6. 5KN-ET HV 5kW (HV)</t>
   </si>
 </sst>
 </file>
@@ -1126,7 +1120,7 @@
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1432,43 +1426,27 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F3" s="6">
-        <v>3</v>
-      </c>
-      <c r="G3" s="7">
-        <v>3690.16</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>73</v>
-      </c>
+      <c r="A3" s="4"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="4"/>
     </row>
     <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>69</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C4" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>71</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>72</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>38</v>
@@ -1477,10 +1455,10 @@
         <v>5</v>
       </c>
       <c r="G4" s="11">
-        <v>3948.39</v>
+        <v>3316.93</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1488,13 +1466,13 @@
         <v>69</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>72</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>38</v>
@@ -1503,62 +1481,46 @@
         <v>6</v>
       </c>
       <c r="G5" s="7">
-        <v>4281.3500000000004</v>
+        <v>3462.34</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="F6" s="10">
-        <v>6</v>
-      </c>
-      <c r="G6" s="11">
-        <v>2859.32</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>73</v>
-      </c>
+      <c r="A6" s="8"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="8"/>
     </row>
     <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>69</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>78</v>
+        <v>164</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>40</v>
       </c>
       <c r="F7" s="6">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="G7" s="7">
-        <v>4951.16</v>
+        <v>3663.64</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1566,13 +1528,13 @@
         <v>69</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>40</v>
@@ -1581,10 +1543,10 @@
         <v>8</v>
       </c>
       <c r="G8" s="11">
-        <v>5533.45</v>
+        <v>4628.87</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1592,13 +1554,13 @@
         <v>69</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>40</v>
@@ -1607,10 +1569,10 @@
         <v>10</v>
       </c>
       <c r="G9" s="7">
-        <v>5848</v>
+        <v>4986.21</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1618,13 +1580,13 @@
         <v>69</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>40</v>
@@ -1633,10 +1595,10 @@
         <v>15</v>
       </c>
       <c r="G10" s="11">
-        <v>8937.82</v>
+        <v>6806.82</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1644,13 +1606,13 @@
         <v>69</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>40</v>
@@ -1659,10 +1621,10 @@
         <v>20</v>
       </c>
       <c r="G11" s="7">
-        <v>10446.75</v>
+        <v>10796.01</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1670,13 +1632,13 @@
         <v>69</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>40</v>
@@ -1685,24 +1647,24 @@
         <v>25</v>
       </c>
       <c r="G12" s="11">
-        <v>12165.88</v>
+        <v>14485.48</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C13" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>72</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>54</v>
@@ -1714,21 +1676,21 @@
         <v>3058</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C14" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" s="8" t="s">
         <v>71</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>72</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>54</v>
@@ -1740,21 +1702,21 @@
         <v>3090</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C15" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>72</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>54</v>
@@ -1766,21 +1728,21 @@
         <v>3152</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C16" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" s="8" t="s">
         <v>71</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>72</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>54</v>
@@ -1792,21 +1754,21 @@
         <v>3082</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C17" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>71</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>72</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>54</v>
@@ -1818,21 +1780,21 @@
         <v>3226</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C18" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" s="8" t="s">
         <v>71</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>72</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>54</v>
@@ -1844,21 +1806,21 @@
         <v>4527</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C19" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" s="8" t="s">
         <v>71</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>72</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>54</v>
@@ -1870,21 +1832,21 @@
         <v>6315</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C20" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>71</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>72</v>
       </c>
       <c r="E20" s="8" t="s">
         <v>54</v>
@@ -1896,21 +1858,21 @@
         <v>6858</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C21" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" s="8" t="s">
         <v>71</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>72</v>
       </c>
       <c r="E21" s="8" t="s">
         <v>54</v>
@@ -1922,21 +1884,21 @@
         <v>7297</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C22" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22" s="8" t="s">
         <v>71</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>72</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>54</v>
@@ -1948,21 +1910,21 @@
         <v>8190</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C23" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" s="8" t="s">
         <v>71</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>72</v>
       </c>
       <c r="E23" s="8" t="s">
         <v>54</v>
@@ -1974,21 +1936,21 @@
         <v>8019</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E24" s="8" t="s">
         <v>54</v>
@@ -2000,21 +1962,21 @@
         <v>6294</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>54</v>
@@ -2026,21 +1988,21 @@
         <v>6538</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>88</v>
-      </c>
       <c r="C26" s="8" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E26" s="8" t="s">
         <v>54</v>
@@ -2052,21 +2014,21 @@
         <v>6790</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>54</v>
@@ -2078,21 +2040,21 @@
         <v>7783</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E28" s="8" t="s">
         <v>56</v>
@@ -2104,21 +2066,21 @@
         <v>4903</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E29" s="8" t="s">
         <v>56</v>
@@ -2130,21 +2092,21 @@
         <v>4590</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E30" s="8" t="s">
         <v>56</v>
@@ -2156,21 +2118,21 @@
         <v>4841</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E31" s="8" t="s">
         <v>56</v>
@@ -2182,21 +2144,21 @@
         <v>5144</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E32" s="8" t="s">
         <v>56</v>
@@ -2208,21 +2170,21 @@
         <v>5646</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E33" s="8" t="s">
         <v>56</v>
@@ -2234,21 +2196,21 @@
         <v>5802</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E34" s="8" t="s">
         <v>56</v>
@@ -2260,21 +2222,21 @@
         <v>5933</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E35" s="8" t="s">
         <v>56</v>
@@ -2286,21 +2248,21 @@
         <v>6116</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>56</v>
@@ -2312,21 +2274,21 @@
         <v>6268</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E37" s="8" t="s">
         <v>56</v>
@@ -2338,21 +2300,21 @@
         <v>6618</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>56</v>
@@ -2364,12 +2326,12 @@
         <v>8217</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B39" s="9"/>
       <c r="C39" s="8"/>
@@ -2381,7 +2343,7 @@
     </row>
     <row r="40" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="4"/>
@@ -2393,7 +2355,7 @@
     </row>
     <row r="41" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B41" s="9"/>
       <c r="C41" s="8"/>
@@ -2405,7 +2367,7 @@
     </row>
     <row r="42" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="4"/>
@@ -2417,7 +2379,7 @@
     </row>
     <row r="43" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B43" s="9"/>
       <c r="C43" s="8"/>
@@ -2429,7 +2391,7 @@
     </row>
     <row r="44" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B44" s="9"/>
       <c r="C44" s="8"/>
@@ -2441,7 +2403,7 @@
     </row>
     <row r="45" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="4"/>
@@ -2453,7 +2415,7 @@
     </row>
     <row r="46" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B46" s="9"/>
       <c r="C46" s="8"/>
@@ -2465,7 +2427,7 @@
     </row>
     <row r="47" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="4"/>
@@ -2477,7 +2439,7 @@
     </row>
     <row r="48" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B48" s="9"/>
       <c r="C48" s="8"/>
@@ -2489,7 +2451,7 @@
     </row>
     <row r="49" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="4"/>
@@ -2501,7 +2463,7 @@
     </row>
     <row r="50" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B50" s="9"/>
       <c r="C50" s="8"/>
@@ -2513,7 +2475,7 @@
     </row>
     <row r="51" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="4"/>
@@ -2836,7 +2798,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
@@ -2853,13 +2815,13 @@
         <v>62</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>67</v>
@@ -2873,10 +2835,10 @@
         <v>69</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D3" s="15">
         <v>5.4</v>
@@ -2888,7 +2850,7 @@
         <v>4756.57</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2896,10 +2858,10 @@
         <v>69</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D4" s="10">
         <v>5</v>
@@ -2911,7 +2873,7 @@
         <v>3665.14</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2919,10 +2881,10 @@
         <v>69</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D5" s="15">
         <v>5</v>
@@ -2934,7 +2896,7 @@
         <v>3603.42</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2942,10 +2904,10 @@
         <v>69</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D6" s="10">
         <v>5</v>
@@ -2957,64 +2919,64 @@
         <v>6952.27</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D7" s="15">
         <v>0</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F7" s="17">
         <v>3262.23</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>101</v>
-      </c>
       <c r="C8" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D8" s="10">
         <v>5</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F8" s="11">
         <v>8200</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D9" s="15">
         <v>5.12</v>
@@ -3026,18 +2988,18 @@
         <v>3267</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D10" s="10">
         <v>10.24</v>
@@ -3049,18 +3011,18 @@
         <v>6769</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D11" s="10">
         <v>5.12</v>
@@ -3072,18 +3034,18 @@
         <v>3492</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D12" s="15">
         <v>14.33</v>
@@ -3095,31 +3057,17 @@
         <v>8777</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D13" s="10">
-        <v>16.07</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="F13" s="11">
-        <v>8978</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>73</v>
-      </c>
+      <c r="A13" s="8"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="8"/>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>
@@ -3223,7 +3171,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F213540-DFB1-4AE5-8B23-D983343261EE}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="14.140625" customWidth="1"/>
@@ -3232,15 +3180,15 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C2" t="s">
         <v>25</v>
@@ -3248,7 +3196,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B3">
         <v>445</v>
@@ -3259,13 +3207,24 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B4">
         <v>460</v>
       </c>
       <c r="C4">
         <v>315</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>163</v>
+      </c>
+      <c r="B5">
+        <v>445</v>
+      </c>
+      <c r="C5">
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -3284,166 +3243,166 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B3">
         <v>5000</v>
       </c>
       <c r="C3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B4">
         <v>8430</v>
       </c>
       <c r="C4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B5">
         <v>15190</v>
       </c>
       <c r="C5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B6">
         <v>500</v>
       </c>
       <c r="C6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B7">
         <v>1600</v>
       </c>
       <c r="C7" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B8">
         <v>2500</v>
       </c>
       <c r="C8" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B9">
         <v>2000</v>
       </c>
       <c r="C9" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B10">
         <v>3500</v>
       </c>
       <c r="C10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B12">
         <v>200</v>
       </c>
       <c r="C12" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B13">
         <v>170</v>
       </c>
       <c r="C13" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B14">
         <v>230</v>
       </c>
       <c r="C14" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B15">
         <v>450</v>
       </c>
       <c r="C15" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B16">
         <v>120</v>
       </c>
       <c r="C16" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>

--- a/configurator-fotovoltaic/catalog_produse_pv.xlsx
+++ b/configurator-fotovoltaic/catalog_produse_pv.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tehni\Desktop\Gabi\CLAUDE oferta\Calculatorfotovoltaic\configurator-fotovoltaic\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tehni\Desktop\Gabi\CLAUDE oferta\platforma\configurator-fotovoltaic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5802CF15-6CDC-43AD-B5FD-13C954188240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1446CE6A-8520-4E28-B4B3-79D0E3996E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22650" yWindow="1680" windowWidth="14355" windowHeight="11760" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucțiuni" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="167">
   <si>
     <t>CATALOG PRODUSE PV — Ghid de utilizare</t>
   </si>
@@ -532,6 +532,12 @@
   </si>
   <si>
     <t>Invertor trifazat Goodwe GW6. 5KN-ET HV 5kW (HV)</t>
+  </si>
+  <si>
+    <t>Trina bif 505 w</t>
+  </si>
+  <si>
+    <t>Trina bif 500 w</t>
   </si>
 </sst>
 </file>
@@ -781,6 +787,9 @@
     <xf numFmtId="4" fontId="9" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -795,9 +804,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1075,18 +1081,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
     </row>
     <row r="3" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
     </row>
     <row r="4" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
@@ -1132,11 +1138,11 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="26" t="s">
+      <c r="A10" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
@@ -1203,11 +1209,11 @@
       </c>
     </row>
     <row r="20" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="27" t="s">
+      <c r="A20" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
     </row>
     <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
@@ -1266,11 +1272,11 @@
       </c>
     </row>
     <row r="29" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="28" t="s">
+      <c r="A29" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
     </row>
     <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
@@ -1388,16 +1394,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
     </row>
     <row r="2" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -3171,7 +3177,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F213540-DFB1-4AE5-8B23-D983343261EE}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="14.140625" customWidth="1"/>
@@ -3225,6 +3231,28 @@
       </c>
       <c r="C5">
         <v>320</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>166</v>
+      </c>
+      <c r="B6">
+        <v>500</v>
+      </c>
+      <c r="C6">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>165</v>
+      </c>
+      <c r="B7">
+        <v>505</v>
+      </c>
+      <c r="C7">
+        <v>356</v>
       </c>
     </row>
   </sheetData>

--- a/configurator-fotovoltaic/catalog_produse_pv.xlsx
+++ b/configurator-fotovoltaic/catalog_produse_pv.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tehni\Desktop\Gabi\CLAUDE oferta\platforma\configurator-fotovoltaic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1446CE6A-8520-4E28-B4B3-79D0E3996E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9CDAA0A-6A77-454A-8BB1-F7F8A9A6E7AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="435" yWindow="1125" windowWidth="14355" windowHeight="11760" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucțiuni" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="171">
   <si>
     <t>CATALOG PRODUSE PV — Ghid de utilizare</t>
   </si>
@@ -538,6 +538,18 @@
   </si>
   <si>
     <t>Trina bif 500 w</t>
+  </si>
+  <si>
+    <t>Invertor trifazat Goodwe GW29,9 k0et</t>
+  </si>
+  <si>
+    <t>goodwe_fv</t>
+  </si>
+  <si>
+    <t>Invertor Monofaza Goodwe EH6000w</t>
+  </si>
+  <si>
+    <t>Mono</t>
   </si>
 </sst>
 </file>
@@ -787,9 +799,6 @@
     <xf numFmtId="4" fontId="9" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -804,6 +813,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1081,18 +1093,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
     </row>
     <row r="3" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
     </row>
     <row r="4" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
@@ -1138,11 +1150,11 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
@@ -1209,11 +1221,11 @@
       </c>
     </row>
     <row r="20" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="28" t="s">
+      <c r="A20" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
     </row>
     <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
@@ -1272,11 +1284,11 @@
       </c>
     </row>
     <row r="29" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="29" t="s">
+      <c r="A29" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
     </row>
     <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
@@ -1381,7 +1393,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H96"/>
+  <dimension ref="A1:H97"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1394,16 +1406,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
     </row>
     <row r="2" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -1494,14 +1506,30 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="8"/>
+      <c r="A6" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="10">
+        <v>6</v>
+      </c>
+      <c r="G6" s="11">
+        <v>2803</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -1634,132 +1662,132 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F12" s="6">
+        <v>29.9</v>
+      </c>
+      <c r="G12" s="7">
+        <v>14486</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C13" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D13" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E13" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F13" s="10">
         <v>25</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G13" s="11">
         <v>14485.48</v>
       </c>
-      <c r="H12" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="H13" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B14" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C14" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D14" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E14" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F14" s="6">
         <v>3</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G14" s="7">
         <v>3058</v>
       </c>
-      <c r="H13" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
+      <c r="H14" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B15" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C15" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D15" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E15" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F15" s="10">
         <v>3.6</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G15" s="11">
         <v>3090</v>
       </c>
-      <c r="H14" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+      <c r="H15" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B16" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C16" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D16" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E16" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F16" s="6">
         <v>4.5999999999999996</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G16" s="7">
         <v>3152</v>
       </c>
-      <c r="H15" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F16" s="10">
-        <v>5</v>
-      </c>
-      <c r="G16" s="11">
-        <v>3082</v>
-      </c>
-      <c r="H16" s="4" t="s">
+      <c r="H16" s="8" t="s">
         <v>72</v>
       </c>
     </row>
@@ -1768,7 +1796,7 @@
         <v>82</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>70</v>
@@ -1780,10 +1808,10 @@
         <v>54</v>
       </c>
       <c r="F17" s="10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G17" s="11">
-        <v>3226</v>
+        <v>3082</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>72</v>
@@ -1794,7 +1822,7 @@
         <v>82</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>70</v>
@@ -1806,10 +1834,10 @@
         <v>54</v>
       </c>
       <c r="F18" s="10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G18" s="11">
-        <v>4527</v>
+        <v>3226</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>72</v>
@@ -1820,7 +1848,7 @@
         <v>82</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>70</v>
@@ -1832,10 +1860,10 @@
         <v>54</v>
       </c>
       <c r="F19" s="10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G19" s="11">
-        <v>6315</v>
+        <v>4527</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>72</v>
@@ -1846,7 +1874,7 @@
         <v>82</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>70</v>
@@ -1857,11 +1885,11 @@
       <c r="E20" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F20" s="19">
-        <v>12</v>
-      </c>
-      <c r="G20" s="20">
-        <v>6858</v>
+      <c r="F20" s="10">
+        <v>10</v>
+      </c>
+      <c r="G20" s="11">
+        <v>6315</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>72</v>
@@ -1872,7 +1900,7 @@
         <v>82</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>70</v>
@@ -1884,10 +1912,10 @@
         <v>54</v>
       </c>
       <c r="F21" s="19">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G21" s="20">
-        <v>7297</v>
+        <v>6858</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>72</v>
@@ -1898,7 +1926,7 @@
         <v>82</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>70</v>
@@ -1910,10 +1938,10 @@
         <v>54</v>
       </c>
       <c r="F22" s="19">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G22" s="20">
-        <v>8190</v>
+        <v>7297</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>72</v>
@@ -1924,7 +1952,7 @@
         <v>82</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>70</v>
@@ -1936,10 +1964,10 @@
         <v>54</v>
       </c>
       <c r="F23" s="19">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G23" s="20">
-        <v>8019</v>
+        <v>8190</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>72</v>
@@ -1950,10 +1978,10 @@
         <v>82</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>83</v>
+        <v>144</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>71</v>
@@ -1961,89 +1989,89 @@
       <c r="E24" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F24" s="10">
+      <c r="F24" s="19">
+        <v>18</v>
+      </c>
+      <c r="G24" s="20">
+        <v>8019</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F25" s="10">
         <v>8</v>
       </c>
-      <c r="G24" s="11">
+      <c r="G25" s="11">
         <v>6294</v>
       </c>
-      <c r="H24" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+      <c r="H25" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B26" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C26" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D26" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E26" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F25" s="6">
+      <c r="F26" s="6">
         <v>10</v>
       </c>
-      <c r="G25" s="7">
+      <c r="G26" s="7">
         <v>6538</v>
       </c>
-      <c r="H25" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
+      <c r="H26" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B27" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C27" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D27" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E27" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F26" s="10">
+      <c r="F27" s="10">
         <v>12</v>
       </c>
-      <c r="G26" s="11">
+      <c r="G27" s="11">
         <v>6790</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F27" s="6">
-        <v>15</v>
-      </c>
-      <c r="G27" s="7">
-        <v>7783</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>72</v>
@@ -2053,23 +2081,23 @@
       <c r="A28" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B28" s="21" t="s">
-        <v>145</v>
+      <c r="B28" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>76</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F28" s="19">
-        <v>5</v>
-      </c>
-      <c r="G28" s="20">
-        <v>4903</v>
+        <v>71</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F28" s="6">
+        <v>15</v>
+      </c>
+      <c r="G28" s="7">
+        <v>7783</v>
       </c>
       <c r="H28" s="4" t="s">
         <v>72</v>
@@ -2080,7 +2108,7 @@
         <v>82</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>76</v>
@@ -2091,11 +2119,11 @@
       <c r="E29" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F29" s="22">
-        <v>6</v>
-      </c>
-      <c r="G29" s="23">
-        <v>4590</v>
+      <c r="F29" s="19">
+        <v>5</v>
+      </c>
+      <c r="G29" s="20">
+        <v>4903</v>
       </c>
       <c r="H29" s="4" t="s">
         <v>72</v>
@@ -2106,7 +2134,7 @@
         <v>82</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>76</v>
@@ -2117,11 +2145,11 @@
       <c r="E30" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F30" s="19">
-        <v>8</v>
-      </c>
-      <c r="G30" s="20">
-        <v>4841</v>
+      <c r="F30" s="22">
+        <v>6</v>
+      </c>
+      <c r="G30" s="23">
+        <v>4590</v>
       </c>
       <c r="H30" s="4" t="s">
         <v>72</v>
@@ -2132,7 +2160,7 @@
         <v>82</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>76</v>
@@ -2143,11 +2171,11 @@
       <c r="E31" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F31" s="22">
-        <v>10</v>
-      </c>
-      <c r="G31" s="23">
-        <v>5144</v>
+      <c r="F31" s="19">
+        <v>8</v>
+      </c>
+      <c r="G31" s="20">
+        <v>4841</v>
       </c>
       <c r="H31" s="4" t="s">
         <v>72</v>
@@ -2157,10 +2185,10 @@
       <c r="A32" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B32" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="C32" s="8" t="s">
+      <c r="B32" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="C32" s="4" t="s">
         <v>76</v>
       </c>
       <c r="D32" s="4" t="s">
@@ -2169,11 +2197,11 @@
       <c r="E32" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F32" s="10">
-        <v>5</v>
-      </c>
-      <c r="G32" s="11">
-        <v>5646</v>
+      <c r="F32" s="22">
+        <v>10</v>
+      </c>
+      <c r="G32" s="23">
+        <v>5144</v>
       </c>
       <c r="H32" s="4" t="s">
         <v>72</v>
@@ -2184,7 +2212,7 @@
         <v>82</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>76</v>
@@ -2196,10 +2224,10 @@
         <v>56</v>
       </c>
       <c r="F33" s="10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G33" s="11">
-        <v>5802</v>
+        <v>5646</v>
       </c>
       <c r="H33" s="4" t="s">
         <v>72</v>
@@ -2210,7 +2238,7 @@
         <v>82</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>76</v>
@@ -2222,10 +2250,10 @@
         <v>56</v>
       </c>
       <c r="F34" s="10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G34" s="11">
-        <v>5933</v>
+        <v>5802</v>
       </c>
       <c r="H34" s="4" t="s">
         <v>72</v>
@@ -2236,7 +2264,7 @@
         <v>82</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>76</v>
@@ -2248,10 +2276,10 @@
         <v>56</v>
       </c>
       <c r="F35" s="10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G35" s="11">
-        <v>6116</v>
+        <v>5933</v>
       </c>
       <c r="H35" s="4" t="s">
         <v>72</v>
@@ -2262,138 +2290,152 @@
         <v>82</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="C36" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C36" s="8" t="s">
         <v>76</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F36" s="6">
+      <c r="F36" s="10">
+        <v>10</v>
+      </c>
+      <c r="G36" s="11">
+        <v>6116</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F37" s="6">
         <v>12</v>
       </c>
-      <c r="G36" s="7">
+      <c r="G37" s="7">
         <v>6268</v>
       </c>
-      <c r="H36" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="8" t="s">
+      <c r="H37" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B38" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C38" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="D37" s="8" t="s">
+      <c r="D38" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="E37" s="8" t="s">
+      <c r="E38" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F37" s="10">
+      <c r="F38" s="10">
         <v>15</v>
       </c>
-      <c r="G37" s="11">
+      <c r="G38" s="11">
         <v>6618</v>
       </c>
-      <c r="H37" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
+      <c r="H38" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B39" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C39" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D39" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E39" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F38" s="6">
+      <c r="F39" s="6">
         <v>20</v>
       </c>
-      <c r="G38" s="7">
+      <c r="G39" s="7">
         <v>8217</v>
       </c>
-      <c r="H38" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="B39" s="9"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="4"/>
+      <c r="H39" s="4" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="40" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="B40" s="5"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="8"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="10"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="4"/>
     </row>
     <row r="41" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="B41" s="9"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="10"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="4"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="7"/>
+      <c r="H41" s="8"/>
     </row>
     <row r="42" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="B42" s="5"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="7"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="11"/>
       <c r="H42" s="4"/>
     </row>
     <row r="43" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="B43" s="9"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="8"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="7"/>
+      <c r="H43" s="4"/>
     </row>
     <row r="44" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
@@ -2411,357 +2453,368 @@
       <c r="A45" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="B45" s="5"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="6"/>
-      <c r="G45" s="7"/>
-      <c r="H45" s="4"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="10"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="8"/>
     </row>
     <row r="46" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="B46" s="9"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="10"/>
-      <c r="G46" s="11"/>
-      <c r="H46" s="8"/>
+      <c r="B46" s="5"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="7"/>
+      <c r="H46" s="4"/>
     </row>
     <row r="47" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="B47" s="5"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="4"/>
-      <c r="F47" s="6"/>
-      <c r="G47" s="7"/>
-      <c r="H47" s="4"/>
+      <c r="B47" s="9"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="10"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="8"/>
     </row>
     <row r="48" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="B48" s="9"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="10"/>
-      <c r="G48" s="11"/>
-      <c r="H48" s="8"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="7"/>
+      <c r="H48" s="4"/>
     </row>
     <row r="49" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="B49" s="5"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="6"/>
-      <c r="G49" s="7"/>
-      <c r="H49" s="4"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="8"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="8"/>
+      <c r="F49" s="10"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="8"/>
     </row>
     <row r="50" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="B50" s="9"/>
-      <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="10"/>
-      <c r="G50" s="11"/>
-      <c r="H50" s="8"/>
+      <c r="B50" s="5"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="7"/>
+      <c r="H50" s="4"/>
     </row>
     <row r="51" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="B51" s="5"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="6"/>
-      <c r="G51" s="7"/>
-      <c r="H51" s="4"/>
+      <c r="B51" s="9"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="10"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="8"/>
     </row>
     <row r="52" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="8"/>
-      <c r="B52" s="9"/>
-      <c r="C52" s="8"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="10"/>
-      <c r="G52" s="11"/>
-      <c r="H52" s="8"/>
+      <c r="A52" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B52" s="5"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="7"/>
+      <c r="H52" s="4"/>
     </row>
     <row r="53" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="4"/>
-      <c r="B53" s="5"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="6"/>
-      <c r="G53" s="7"/>
-      <c r="H53" s="4"/>
+      <c r="A53" s="8"/>
+      <c r="B53" s="9"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="10"/>
+      <c r="G53" s="11"/>
+      <c r="H53" s="8"/>
     </row>
     <row r="54" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="8"/>
-      <c r="B54" s="9"/>
-      <c r="C54" s="8"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="10"/>
-      <c r="G54" s="11"/>
-      <c r="H54" s="8"/>
+      <c r="A54" s="4"/>
+      <c r="B54" s="5"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="7"/>
+      <c r="H54" s="4"/>
     </row>
     <row r="55" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="4"/>
-      <c r="B55" s="5"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="4"/>
-      <c r="E55" s="4"/>
-      <c r="F55" s="6"/>
-      <c r="G55" s="7"/>
-      <c r="H55" s="4"/>
+      <c r="A55" s="8"/>
+      <c r="B55" s="9"/>
+      <c r="C55" s="8"/>
+      <c r="D55" s="8"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="10"/>
+      <c r="G55" s="11"/>
+      <c r="H55" s="8"/>
     </row>
     <row r="56" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="8"/>
-      <c r="B56" s="9"/>
-      <c r="C56" s="8"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="10"/>
-      <c r="G56" s="11"/>
-      <c r="H56" s="8"/>
+      <c r="A56" s="4"/>
+      <c r="B56" s="5"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="6"/>
+      <c r="G56" s="7"/>
+      <c r="H56" s="4"/>
     </row>
     <row r="57" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="4"/>
-      <c r="B57" s="5"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="6"/>
-      <c r="G57" s="7"/>
-      <c r="H57" s="4"/>
+      <c r="A57" s="8"/>
+      <c r="B57" s="9"/>
+      <c r="C57" s="8"/>
+      <c r="D57" s="8"/>
+      <c r="E57" s="8"/>
+      <c r="F57" s="10"/>
+      <c r="G57" s="11"/>
+      <c r="H57" s="8"/>
     </row>
     <row r="58" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="8"/>
-      <c r="B58" s="9"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="10"/>
-      <c r="G58" s="11"/>
-      <c r="H58" s="8"/>
+      <c r="A58" s="4"/>
+      <c r="B58" s="5"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="6"/>
+      <c r="G58" s="7"/>
+      <c r="H58" s="4"/>
     </row>
     <row r="59" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="4"/>
-      <c r="B59" s="5"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="4"/>
-      <c r="E59" s="4"/>
-      <c r="F59" s="6"/>
-      <c r="G59" s="7"/>
-      <c r="H59" s="4"/>
+      <c r="A59" s="8"/>
+      <c r="B59" s="9"/>
+      <c r="C59" s="8"/>
+      <c r="D59" s="8"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="10"/>
+      <c r="G59" s="11"/>
+      <c r="H59" s="8"/>
     </row>
     <row r="60" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="8"/>
-      <c r="B60" s="9"/>
-      <c r="C60" s="8"/>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="10"/>
-      <c r="G60" s="11"/>
-      <c r="H60" s="8"/>
+      <c r="A60" s="4"/>
+      <c r="B60" s="5"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="6"/>
+      <c r="G60" s="7"/>
+      <c r="H60" s="4"/>
     </row>
     <row r="61" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="4"/>
-      <c r="B61" s="5"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="4"/>
-      <c r="E61" s="4"/>
-      <c r="F61" s="6"/>
-      <c r="G61" s="7"/>
-      <c r="H61" s="4"/>
+      <c r="A61" s="8"/>
+      <c r="B61" s="9"/>
+      <c r="C61" s="8"/>
+      <c r="D61" s="8"/>
+      <c r="E61" s="8"/>
+      <c r="F61" s="10"/>
+      <c r="G61" s="11"/>
+      <c r="H61" s="8"/>
     </row>
     <row r="62" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="8"/>
-      <c r="B62" s="9"/>
-      <c r="C62" s="8"/>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
-      <c r="F62" s="10"/>
-      <c r="G62" s="11"/>
-      <c r="H62" s="8"/>
+      <c r="A62" s="4"/>
+      <c r="B62" s="5"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="6"/>
+      <c r="G62" s="7"/>
+      <c r="H62" s="4"/>
     </row>
     <row r="63" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="4"/>
-      <c r="B63" s="5"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="4"/>
-      <c r="E63" s="4"/>
-      <c r="F63" s="6"/>
-      <c r="G63" s="7"/>
-      <c r="H63" s="4"/>
+      <c r="A63" s="8"/>
+      <c r="B63" s="9"/>
+      <c r="C63" s="8"/>
+      <c r="D63" s="8"/>
+      <c r="E63" s="8"/>
+      <c r="F63" s="10"/>
+      <c r="G63" s="11"/>
+      <c r="H63" s="8"/>
     </row>
     <row r="64" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="8"/>
-      <c r="B64" s="9"/>
-      <c r="C64" s="8"/>
-      <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
-      <c r="F64" s="10"/>
-      <c r="G64" s="11"/>
-      <c r="H64" s="8"/>
+      <c r="A64" s="4"/>
+      <c r="B64" s="5"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="7"/>
+      <c r="H64" s="4"/>
     </row>
     <row r="65" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="4"/>
-      <c r="B65" s="5"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="4"/>
-      <c r="E65" s="4"/>
-      <c r="F65" s="6"/>
-      <c r="G65" s="7"/>
-      <c r="H65" s="4"/>
+      <c r="A65" s="8"/>
+      <c r="B65" s="9"/>
+      <c r="C65" s="8"/>
+      <c r="D65" s="8"/>
+      <c r="E65" s="8"/>
+      <c r="F65" s="10"/>
+      <c r="G65" s="11"/>
+      <c r="H65" s="8"/>
     </row>
     <row r="66" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="8"/>
-      <c r="B66" s="9"/>
-      <c r="C66" s="8"/>
-      <c r="D66" s="8"/>
-      <c r="E66" s="8"/>
-      <c r="F66" s="10"/>
-      <c r="G66" s="11"/>
-      <c r="H66" s="8"/>
+      <c r="A66" s="4"/>
+      <c r="B66" s="5"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="6"/>
+      <c r="G66" s="7"/>
+      <c r="H66" s="4"/>
     </row>
     <row r="67" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="4"/>
-      <c r="B67" s="5"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="4"/>
-      <c r="E67" s="4"/>
-      <c r="F67" s="6"/>
-      <c r="G67" s="7"/>
-      <c r="H67" s="4"/>
+      <c r="A67" s="8"/>
+      <c r="B67" s="9"/>
+      <c r="C67" s="8"/>
+      <c r="D67" s="8"/>
+      <c r="E67" s="8"/>
+      <c r="F67" s="10"/>
+      <c r="G67" s="11"/>
+      <c r="H67" s="8"/>
     </row>
     <row r="68" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="8"/>
-      <c r="B68" s="9"/>
-      <c r="C68" s="8"/>
-      <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="10"/>
-      <c r="G68" s="11"/>
-      <c r="H68" s="8"/>
+      <c r="A68" s="4"/>
+      <c r="B68" s="5"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="6"/>
+      <c r="G68" s="7"/>
+      <c r="H68" s="4"/>
     </row>
     <row r="69" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="4"/>
-      <c r="B69" s="5"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="4"/>
-      <c r="E69" s="4"/>
-      <c r="F69" s="6"/>
-      <c r="G69" s="7"/>
-      <c r="H69" s="4"/>
+      <c r="A69" s="8"/>
+      <c r="B69" s="9"/>
+      <c r="C69" s="8"/>
+      <c r="D69" s="8"/>
+      <c r="E69" s="8"/>
+      <c r="F69" s="10"/>
+      <c r="G69" s="11"/>
+      <c r="H69" s="8"/>
     </row>
     <row r="70" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="8"/>
-      <c r="B70" s="9"/>
-      <c r="C70" s="8"/>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="10"/>
-      <c r="G70" s="11"/>
-      <c r="H70" s="8"/>
+      <c r="A70" s="4"/>
+      <c r="B70" s="5"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="6"/>
+      <c r="G70" s="7"/>
+      <c r="H70" s="4"/>
     </row>
     <row r="71" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="4"/>
-      <c r="B71" s="5"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="4"/>
-      <c r="E71" s="4"/>
-      <c r="F71" s="6"/>
-      <c r="G71" s="7"/>
-      <c r="H71" s="4"/>
+      <c r="A71" s="8"/>
+      <c r="B71" s="9"/>
+      <c r="C71" s="8"/>
+      <c r="D71" s="8"/>
+      <c r="E71" s="8"/>
+      <c r="F71" s="10"/>
+      <c r="G71" s="11"/>
+      <c r="H71" s="8"/>
     </row>
     <row r="72" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="8"/>
-      <c r="B72" s="9"/>
-      <c r="C72" s="8"/>
-      <c r="D72" s="8"/>
-      <c r="E72" s="8"/>
-      <c r="F72" s="10"/>
-      <c r="G72" s="11"/>
-      <c r="H72" s="8"/>
+      <c r="A72" s="4"/>
+      <c r="B72" s="5"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="6"/>
+      <c r="G72" s="7"/>
+      <c r="H72" s="4"/>
     </row>
     <row r="73" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="4"/>
-      <c r="B73" s="5"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="4"/>
-      <c r="E73" s="4"/>
-      <c r="F73" s="6"/>
-      <c r="G73" s="7"/>
-      <c r="H73" s="4"/>
+      <c r="A73" s="8"/>
+      <c r="B73" s="9"/>
+      <c r="C73" s="8"/>
+      <c r="D73" s="8"/>
+      <c r="E73" s="8"/>
+      <c r="F73" s="10"/>
+      <c r="G73" s="11"/>
+      <c r="H73" s="8"/>
     </row>
     <row r="74" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="8"/>
-      <c r="B74" s="9"/>
-      <c r="C74" s="8"/>
-      <c r="D74" s="8"/>
-      <c r="E74" s="8"/>
-      <c r="F74" s="10"/>
-      <c r="G74" s="11"/>
-      <c r="H74" s="8"/>
+      <c r="A74" s="4"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="6"/>
+      <c r="G74" s="7"/>
+      <c r="H74" s="4"/>
     </row>
     <row r="75" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="4"/>
-      <c r="B75" s="5"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="4"/>
-      <c r="E75" s="4"/>
-      <c r="F75" s="6"/>
-      <c r="G75" s="7"/>
-      <c r="H75" s="4"/>
+      <c r="A75" s="8"/>
+      <c r="B75" s="9"/>
+      <c r="C75" s="8"/>
+      <c r="D75" s="8"/>
+      <c r="E75" s="8"/>
+      <c r="F75" s="10"/>
+      <c r="G75" s="11"/>
+      <c r="H75" s="8"/>
     </row>
     <row r="76" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="8"/>
-      <c r="B76" s="9"/>
-      <c r="C76" s="8"/>
-      <c r="D76" s="8"/>
-      <c r="E76" s="8"/>
-      <c r="F76" s="10"/>
-      <c r="G76" s="11"/>
-      <c r="H76" s="8"/>
+      <c r="A76" s="4"/>
+      <c r="B76" s="5"/>
+      <c r="C76" s="4"/>
+      <c r="D76" s="4"/>
+      <c r="E76" s="4"/>
+      <c r="F76" s="6"/>
+      <c r="G76" s="7"/>
+      <c r="H76" s="4"/>
     </row>
     <row r="77" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="4"/>
-      <c r="B77" s="5"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="4"/>
-      <c r="E77" s="4"/>
-      <c r="F77" s="6"/>
-      <c r="G77" s="7"/>
-      <c r="H77" s="4"/>
+      <c r="A77" s="8"/>
+      <c r="B77" s="9"/>
+      <c r="C77" s="8"/>
+      <c r="D77" s="8"/>
+      <c r="E77" s="8"/>
+      <c r="F77" s="10"/>
+      <c r="G77" s="11"/>
+      <c r="H77" s="8"/>
     </row>
     <row r="78" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="8"/>
-      <c r="B78" s="9"/>
-      <c r="C78" s="8"/>
-      <c r="D78" s="8"/>
-      <c r="E78" s="8"/>
-      <c r="F78" s="10"/>
-      <c r="G78" s="11"/>
-      <c r="H78" s="8"/>
-    </row>
-    <row r="79" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="A78" s="4"/>
+      <c r="B78" s="5"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="6"/>
+      <c r="G78" s="7"/>
+      <c r="H78" s="4"/>
+    </row>
+    <row r="79" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="8"/>
+      <c r="B79" s="9"/>
+      <c r="C79" s="8"/>
+      <c r="D79" s="8"/>
+      <c r="E79" s="8"/>
+      <c r="F79" s="10"/>
+      <c r="G79" s="11"/>
+      <c r="H79" s="8"/>
+    </row>
     <row r="80" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="81" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="82" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2779,6 +2832,7 @@
     <row r="94" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="95" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="96" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
